--- a/codebook.xlsx
+++ b/codebook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\世界上最漂亮最可爱最聪明的小仙女\智能汽车性能与安全实验室\总结\word\Bridging prediction accuracy and interpretability A hybrid PSO-XGBoost-MNL model for analyzing injury severity of EB-motor vehicle crashes in China\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74EAB91D-0DAB-49AC-9878-C1959F2F4DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE6CCF4A-3514-43B1-85E3-42E8C4B7BC64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="56">
   <si>
     <r>
       <t>1</t>
@@ -337,6 +337,21 @@
   </si>
   <si>
     <t>4/6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accident classification</t>
+  </si>
+  <si>
+    <t>PI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FI</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -404,13 +419,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -693,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C81"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.83203125" style="2" customWidth="1"/>
@@ -1288,6 +1303,35 @@
       </c>
       <c r="C81" s="1"/>
     </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B84" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B85" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A86" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B86" s="3">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
